--- a/data/trans_orig/IMC_inf_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_R2-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23228</t>
+          <t>23443</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38325</t>
+          <t>37623</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23026</t>
+          <t>23764</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37647</t>
+          <t>37701</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51694</t>
+          <t>50894</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71548</t>
+          <t>71425</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,59%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49354</t>
+          <t>50056</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64451</t>
+          <t>64236</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46393</t>
+          <t>46339</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61014</t>
+          <t>60276</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100171</t>
+          <t>100294</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120025</t>
+          <t>120825</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,36%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18312</t>
+          <t>17922</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31025</t>
+          <t>31048</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20063</t>
+          <t>20498</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32963</t>
+          <t>33130</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41843</t>
+          <t>40712</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61033</t>
+          <t>60001</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,09%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42939</t>
+          <t>42916</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55652</t>
+          <t>56042</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35637</t>
+          <t>35470</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48537</t>
+          <t>48102</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>81531</t>
+          <t>82563</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>100721</t>
+          <t>101852</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>71,44%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12955</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23877</t>
+          <t>24158</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36176</t>
+          <t>36981</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51726</t>
+          <t>51359</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52915</t>
+          <t>53880</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71955</t>
+          <t>72269</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>50,13%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32469</t>
+          <t>32188</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43391</t>
+          <t>43794</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36099</t>
+          <t>36466</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51649</t>
+          <t>50844</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72216</t>
+          <t>71902</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>91256</t>
+          <t>90291</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>62,63%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53273</t>
+          <t>53487</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73559</t>
+          <t>73999</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70677</t>
+          <t>70952</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92258</t>
+          <t>90478</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>129903</t>
+          <t>129340</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>159011</t>
+          <t>158628</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,46%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93621</t>
+          <t>93181</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>113907</t>
+          <t>113693</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74820</t>
+          <t>76600</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>96401</t>
+          <t>96126</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>175247</t>
+          <t>175630</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>204355</t>
+          <t>204918</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,31%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30902</t>
+          <t>31377</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46019</t>
+          <t>46434</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38397</t>
+          <t>39542</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55554</t>
+          <t>55105</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76163</t>
+          <t>73494</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98186</t>
+          <t>96375</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>48,26%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43213</t>
+          <t>42798</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58330</t>
+          <t>57855</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54900</t>
+          <t>55349</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72057</t>
+          <t>70912</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>101500</t>
+          <t>103311</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>123523</t>
+          <t>126192</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>63,2%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12925</t>
+          <t>12386</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24269</t>
+          <t>24149</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26320</t>
+          <t>26092</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38120</t>
+          <t>37486</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41222</t>
+          <t>41909</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59130</t>
+          <t>59352</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,46%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43217</t>
+          <t>43337</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>54561</t>
+          <t>55100</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19452</t>
+          <t>20086</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31252</t>
+          <t>31480</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>65928</t>
+          <t>65706</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>83836</t>
+          <t>83149</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,49%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>177411</t>
+          <t>174278</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>212300</t>
+          <t>210117</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>242025</t>
+          <t>242780</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>279837</t>
+          <t>281005</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>429387</t>
+          <t>428392</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>481067</t>
+          <t>481427</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>329586</t>
+          <t>331769</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>364475</t>
+          <t>367608</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>295733</t>
+          <t>294565</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>333545</t>
+          <t>332790</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>636389</t>
+          <t>636029</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>688069</t>
+          <t>689064</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,66%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23923</t>
+          <t>23560</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37867</t>
+          <t>37197</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24681</t>
+          <t>24378</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36691</t>
+          <t>37045</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51511</t>
+          <t>52178</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71037</t>
+          <t>70362</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>53,48%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31202</t>
+          <t>31872</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45146</t>
+          <t>45509</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25805</t>
+          <t>25451</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37815</t>
+          <t>38118</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>60529</t>
+          <t>61204</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80055</t>
+          <t>79388</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,34%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17195</t>
+          <t>17662</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30703</t>
+          <t>30068</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36034</t>
+          <t>36230</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50547</t>
+          <t>50395</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56569</t>
+          <t>57077</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76308</t>
+          <t>76503</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,23%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38781</t>
+          <t>39416</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52289</t>
+          <t>51822</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26443</t>
+          <t>26595</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40956</t>
+          <t>40760</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>70166</t>
+          <t>69971</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>89905</t>
+          <t>89397</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,03%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16687</t>
+          <t>16806</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29067</t>
+          <t>28549</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23990</t>
+          <t>24428</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37580</t>
+          <t>37445</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43163</t>
+          <t>45343</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61798</t>
+          <t>62056</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,55%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35864</t>
+          <t>36382</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48244</t>
+          <t>48125</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25307</t>
+          <t>25442</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38897</t>
+          <t>38459</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66020</t>
+          <t>65762</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>84655</t>
+          <t>82475</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>64,53%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53001</t>
+          <t>52757</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71781</t>
+          <t>72526</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82779</t>
+          <t>83106</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105203</t>
+          <t>105011</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>141278</t>
+          <t>141674</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>170080</t>
+          <t>169828</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,78%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71452</t>
+          <t>70707</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90232</t>
+          <t>90476</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67325</t>
+          <t>67517</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>89749</t>
+          <t>89422</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>145681</t>
+          <t>145933</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>174483</t>
+          <t>174087</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,13%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46883</t>
+          <t>46674</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65296</t>
+          <t>64769</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34031</t>
+          <t>33376</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50824</t>
+          <t>50324</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>85616</t>
+          <t>86558</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>109767</t>
+          <t>110641</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>52,01%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49328</t>
+          <t>49855</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67741</t>
+          <t>67950</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47292</t>
+          <t>47792</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64085</t>
+          <t>64740</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>102973</t>
+          <t>102099</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>127124</t>
+          <t>126182</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,31%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>13229</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23353</t>
+          <t>23551</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22580</t>
+          <t>23226</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35365</t>
+          <t>35972</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39863</t>
+          <t>39419</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55745</t>
+          <t>55728</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,5%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17959</t>
+          <t>17761</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28449</t>
+          <t>28083</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21961</t>
+          <t>21354</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34746</t>
+          <t>34100</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>42893</t>
+          <t>42910</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>58775</t>
+          <t>59219</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>60,04%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>194450</t>
+          <t>194869</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>230122</t>
+          <t>230500</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>251076</t>
+          <t>248633</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>288749</t>
+          <t>288436</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>453130</t>
+          <t>454144</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>508181</t>
+          <t>509811</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,35%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>272532</t>
+          <t>272154</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>308204</t>
+          <t>307785</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>241594</t>
+          <t>241907</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>279267</t>
+          <t>281710</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>524816</t>
+          <t>523186</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>579867</t>
+          <t>578853</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,04%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13441</t>
+          <t>13306</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25296</t>
+          <t>24762</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26923</t>
+          <t>26929</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40426</t>
+          <t>40417</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43503</t>
+          <t>42936</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61181</t>
+          <t>62053</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>46,48%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34055</t>
+          <t>34589</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45910</t>
+          <t>46045</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33724</t>
+          <t>33733</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47227</t>
+          <t>47221</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72320</t>
+          <t>71448</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>89998</t>
+          <t>90565</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,84%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12880</t>
+          <t>13080</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25472</t>
+          <t>25257</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28174</t>
+          <t>27872</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43039</t>
+          <t>43423</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44224</t>
+          <t>43344</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63933</t>
+          <t>64019</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54757</t>
+          <t>54972</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67349</t>
+          <t>67149</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49972</t>
+          <t>49588</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>64837</t>
+          <t>65139</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109306</t>
+          <t>109220</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>129015</t>
+          <t>129895</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,98%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10152</t>
+          <t>10044</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20548</t>
+          <t>20326</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21822</t>
+          <t>22348</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35051</t>
+          <t>34824</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35800</t>
+          <t>34972</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52618</t>
+          <t>52016</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>46,82%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28741</t>
+          <t>28963</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39137</t>
+          <t>39245</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26753</t>
+          <t>26980</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39982</t>
+          <t>39456</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58475</t>
+          <t>59077</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>75293</t>
+          <t>76121</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,52%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57749</t>
+          <t>58466</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78847</t>
+          <t>80207</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54256</t>
+          <t>54274</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75125</t>
+          <t>74226</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>119719</t>
+          <t>118631</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148649</t>
+          <t>149075</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,43%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90052</t>
+          <t>88692</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111150</t>
+          <t>110433</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84130</t>
+          <t>85029</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>104999</t>
+          <t>104981</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>179505</t>
+          <t>179079</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>208435</t>
+          <t>209523</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,85%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33412</t>
+          <t>32922</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50044</t>
+          <t>48810</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44889</t>
+          <t>45787</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62178</t>
+          <t>63369</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83897</t>
+          <t>82972</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107177</t>
+          <t>107311</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,02%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60183</t>
+          <t>61417</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76815</t>
+          <t>77305</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51053</t>
+          <t>49862</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68342</t>
+          <t>67444</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>116281</t>
+          <t>116147</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>139561</t>
+          <t>140486</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,87%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11090</t>
+          <t>11153</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21917</t>
+          <t>22404</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21064</t>
+          <t>20602</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32878</t>
+          <t>32736</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34574</t>
+          <t>34556</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50773</t>
+          <t>50242</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,09%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25783</t>
+          <t>25296</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36610</t>
+          <t>36547</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21770</t>
+          <t>21912</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33584</t>
+          <t>34046</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51576</t>
+          <t>52107</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>67775</t>
+          <t>67793</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,24%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>162289</t>
+          <t>162032</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>197523</t>
+          <t>196597</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>225412</t>
+          <t>225554</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>262879</t>
+          <t>263101</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>395956</t>
+          <t>391088</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>447030</t>
+          <t>445110</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>318172</t>
+          <t>319098</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>353406</t>
+          <t>353663</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>293220</t>
+          <t>292998</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>330687</t>
+          <t>330545</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>624764</t>
+          <t>626684</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>675838</t>
+          <t>680706</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,51%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>15128</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29599</t>
+          <t>27926</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21654</t>
+          <t>21340</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39965</t>
+          <t>39444</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41394</t>
+          <t>41144</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63477</t>
+          <t>63845</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63263</t>
+          <t>64936</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77362</t>
+          <t>77734</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70862</t>
+          <t>71383</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89173</t>
+          <t>89487</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>140212</t>
+          <t>139844</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162295</t>
+          <t>162545</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,8%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>18877</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33027</t>
+          <t>32506</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27828</t>
+          <t>27946</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44412</t>
+          <t>44665</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51446</t>
+          <t>50524</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73013</t>
+          <t>72589</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,18%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51437</t>
+          <t>51958</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>66053</t>
+          <t>65587</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>43219</t>
+          <t>42966</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59803</t>
+          <t>59685</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>99082</t>
+          <t>99506</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>120649</t>
+          <t>121571</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>70,64%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10014</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20440</t>
+          <t>19769</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17946</t>
+          <t>17791</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32221</t>
+          <t>31991</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30312</t>
+          <t>30096</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48198</t>
+          <t>47486</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>48,74%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21174</t>
+          <t>21845</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31600</t>
+          <t>31980</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23595</t>
+          <t>23825</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37870</t>
+          <t>38025</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49232</t>
+          <t>49944</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67118</t>
+          <t>67334</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>69,11%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37532</t>
+          <t>38316</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75979</t>
+          <t>76026</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67477</t>
+          <t>68872</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97797</t>
+          <t>96986</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111103</t>
+          <t>109150</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>163689</t>
+          <t>163461</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,15%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>119140</t>
+          <t>119093</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>157587</t>
+          <t>156803</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>85863</t>
+          <t>86674</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>116183</t>
+          <t>114788</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>215090</t>
+          <t>215318</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>267676</t>
+          <t>269629</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>71,18%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>25113</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41692</t>
+          <t>41940</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40843</t>
+          <t>40536</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67450</t>
+          <t>66765</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71440</t>
+          <t>71957</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101751</t>
+          <t>101328</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,17%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54144</t>
+          <t>53896</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71204</t>
+          <t>70723</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71422</t>
+          <t>72107</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>98029</t>
+          <t>98336</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>132956</t>
+          <t>133379</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>163267</t>
+          <t>162750</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,34%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15564</t>
+          <t>15848</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>16775</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30786</t>
+          <t>30849</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24158</t>
+          <t>24902</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42577</t>
+          <t>42392</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44082</t>
+          <t>43798</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53943</t>
+          <t>53885</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49552</t>
+          <t>49653</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>83497</t>
+          <t>83682</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101916</t>
+          <t>101172</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,25%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>136858</t>
+          <t>134018</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>184336</t>
+          <t>184019</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>228255</t>
+          <t>224021</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>278306</t>
+          <t>277476</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>376016</t>
+          <t>375980</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>449958</t>
+          <t>449333</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,05%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>385204</t>
+          <t>385521</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>432682</t>
+          <t>435522</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>364928</t>
+          <t>365758</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>414979</t>
+          <t>419213</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>762816</t>
+          <t>763441</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>836758</t>
+          <t>836794</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
